--- a/tables/tables_orig.xlsx
+++ b/tables/tables_orig.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justindudley/MyDocuments/Cube/POCHMANN_FEVER_MAC/PYTHON_Repos/alg_prism_the_whole_enchilada/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/justindudley/dev/cube/Alg_Slice_And_Widen_daddy/alg-slice-and-widen/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2EC7A-8EF9-D94E-A66F-E9AF798E9F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C328D4C-0EAB-4249-A84C-3AF0EAB4B1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1400" windowWidth="32260" windowHeight="16800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
